--- a/kit_validacion/Planilla_comparacion_N25-Valves-Sizing.xlsx
+++ b/kit_validacion/Planilla_comparacion_N25-Valves-Sizing.xlsx
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>93.3</v>
+        <v>80.3</v>
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>80.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F97" s="5" t="n"/>
       <c r="G97" s="5" t="n"/>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>84</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F98" s="5" t="n"/>
       <c r="G98" s="5" t="n"/>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>84</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F99" s="5" t="n"/>
       <c r="G99" s="5" t="n"/>
